--- a/基隆市召會青少年服事人位分組表.xlsx
+++ b/基隆市召會青少年服事人位分組表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Debby\shepherding_materials_dump\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95B6B04C-44E1-44B3-AC4E-9DF607BFCFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F3E11B-1048-4C6F-AC48-630E9131AAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{0A1816D5-F89F-4985-9DA3-AE1053C2CF05}"/>
   </bookViews>
@@ -104,9 +104,6 @@
     <t>李妮</t>
   </si>
   <si>
-    <t>馬來</t>
-  </si>
-  <si>
     <t>恩美</t>
   </si>
   <si>
@@ -150,11 +147,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>苡愛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>服事分組列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>愛</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怡蒨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -162,7 +183,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,6 +197,21 @@
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -253,7 +289,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -268,6 +304,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -612,7 +651,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="4"/>
@@ -633,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -644,7 +683,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>14</v>
@@ -669,7 +708,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -688,10 +727,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -702,7 +741,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -713,7 +752,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -724,7 +763,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -732,21 +771,21 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
